--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sylvester Chung\Desktop\QCF mini tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38675579-28AC-40BD-98BD-E2EE3743D603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C2D8B4-65F0-4934-B44C-288E00790506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-3585" windowWidth="29040" windowHeight="15720" tabRatio="449" xr2:uid="{898A59BC-35DC-4CBF-9EF0-D032C6A7D218}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="51">
   <si>
     <t xml:space="preserve">Date: </t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Senior Project Engineering</t>
+  </si>
+  <si>
+    <t>BASE</t>
   </si>
 </sst>
 </file>
@@ -843,7 +846,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1027,17 +1030,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="28" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="28" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="38" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1134,6 +1128,111 @@
     <xf numFmtId="165" fontId="25" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1185,110 +1284,11 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="4" fontId="28" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1678,33 +1678,33 @@
   <sheetData>
     <row r="1" spans="1:23" ht="21">
       <c r="A1" s="29"/>
-      <c r="B1" s="136" t="s">
+      <c r="B1" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
       <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:23" ht="15.75" customHeight="1">
       <c r="A2" s="29"/>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="144" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
       <c r="I2" s="43" t="s">
         <v>36</v>
       </c>
@@ -1727,9 +1727,9 @@
       <c r="B3" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
       <c r="F3" s="44" t="s">
         <v>36</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="51"/>
-      <c r="N3" s="85"/>
+      <c r="N3" s="82"/>
     </row>
     <row r="4" spans="1:23" ht="18" customHeight="1">
       <c r="A4" s="29"/>
@@ -1795,52 +1795,52 @@
     </row>
     <row r="5" spans="1:23" ht="15.75" customHeight="1">
       <c r="A5" s="29"/>
-      <c r="B5" s="138" t="s">
+      <c r="B5" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="147" t="s">
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="147" t="s">
+      <c r="G5" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="152" t="s">
+      <c r="H5" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="154"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="124"/>
       <c r="N5" s="18"/>
     </row>
     <row r="6" spans="1:23" ht="33" customHeight="1">
       <c r="A6" s="29"/>
-      <c r="B6" s="141"/>
-      <c r="C6" s="142"/>
-      <c r="D6" s="142"/>
-      <c r="E6" s="143"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="155"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="159"/>
-      <c r="K6" s="158"/>
-      <c r="L6" s="157"/>
-      <c r="M6" s="158"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="128"/>
       <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:23" ht="15.6">
       <c r="A7" s="29"/>
-      <c r="B7" s="144"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="151"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="121"/>
       <c r="H7" s="62" t="s">
         <v>37</v>
       </c>
@@ -1853,7 +1853,7 @@
       <c r="K7" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="87" t="s">
+      <c r="L7" s="84" t="s">
         <v>37</v>
       </c>
       <c r="M7" s="66" t="s">
@@ -1862,48 +1862,48 @@
       <c r="N7" s="18"/>
     </row>
     <row r="8" spans="1:23" ht="19.8" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100">
+      <c r="A8" s="96"/>
+      <c r="B8" s="97">
         <v>1</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="95"/>
-      <c r="L8" s="94"/>
-      <c r="M8" s="95"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="152"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="92"/>
       <c r="N8" s="18"/>
-      <c r="O8" s="135"/>
-      <c r="P8" s="135"/>
-      <c r="Q8" s="135"/>
-      <c r="R8" s="135"/>
-      <c r="S8" s="135"/>
-      <c r="T8" s="135"/>
-      <c r="U8" s="135"/>
-      <c r="V8" s="135"/>
-      <c r="W8" s="135"/>
+      <c r="O8" s="105"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="105"/>
+      <c r="R8" s="105"/>
+      <c r="S8" s="105"/>
+      <c r="T8" s="105"/>
+      <c r="U8" s="105"/>
+      <c r="V8" s="105"/>
+      <c r="W8" s="105"/>
     </row>
     <row r="9" spans="1:23" ht="19.8" customHeight="1">
       <c r="A9" s="33"/>
       <c r="B9" s="55">
         <v>2</v>
       </c>
-      <c r="C9" s="122"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="93"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="90"/>
       <c r="N9" s="18"/>
       <c r="O9" s="21"/>
       <c r="P9" s="21"/>
@@ -1920,17 +1920,17 @@
       <c r="B10" s="55">
         <v>3</v>
       </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="93"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="90"/>
       <c r="N10" s="18"/>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
@@ -1959,21 +1959,30 @@
         <v>5</v>
       </c>
       <c r="H11" s="68"/>
-      <c r="I11" s="45"/>
+      <c r="I11" s="45">
+        <f>SUM(I8:I10)</f>
+        <v>0</v>
+      </c>
       <c r="J11" s="37"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="86"/>
-      <c r="O11" s="135"/>
-      <c r="P11" s="135"/>
-      <c r="Q11" s="135"/>
-      <c r="R11" s="135"/>
-      <c r="S11" s="135"/>
-      <c r="T11" s="135"/>
-      <c r="U11" s="135"/>
-      <c r="V11" s="135"/>
-      <c r="W11" s="135"/>
+      <c r="K11" s="45">
+        <f>SUM(K8:K10)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="72"/>
+      <c r="M11" s="45">
+        <f>SUM(M8:M10)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="83"/>
+      <c r="O11" s="105"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="105"/>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="105"/>
+      <c r="U11" s="105"/>
+      <c r="V11" s="105"/>
+      <c r="W11" s="105"/>
     </row>
     <row r="12" spans="1:23" ht="16.5" customHeight="1">
       <c r="A12" s="29"/>
@@ -1994,12 +2003,21 @@
         <v>0.08</v>
       </c>
       <c r="H12" s="68"/>
-      <c r="I12" s="69"/>
+      <c r="I12" s="69">
+        <f>I11*0.08</f>
+        <v>0</v>
+      </c>
       <c r="J12" s="37"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="86"/>
+      <c r="K12" s="69">
+        <f>K11*0.08</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="72"/>
+      <c r="M12" s="69">
+        <f>M11*0.08</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="83"/>
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:23" ht="16.5" customHeight="1">
@@ -2019,12 +2037,21 @@
         <v>7</v>
       </c>
       <c r="H13" s="68"/>
-      <c r="I13" s="45"/>
+      <c r="I13" s="45">
+        <f>I11+I12</f>
+        <v>0</v>
+      </c>
       <c r="J13" s="37"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="73"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="86"/>
+      <c r="K13" s="45">
+        <f>K11+K12</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="72"/>
+      <c r="M13" s="45">
+        <f>M11+M12</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="83"/>
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:23" ht="16.95" customHeight="1">
@@ -2044,12 +2071,14 @@
         <v>25</v>
       </c>
       <c r="H14" s="70"/>
-      <c r="I14" s="45"/>
+      <c r="I14" s="157" t="s">
+        <v>50</v>
+      </c>
       <c r="J14" s="37"/>
       <c r="K14" s="61"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="86"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="83"/>
       <c r="P14" s="3"/>
     </row>
     <row r="15" spans="1:23" ht="16.95" customHeight="1">
@@ -2069,12 +2098,14 @@
         <v>26</v>
       </c>
       <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
+      <c r="I15" s="158" t="s">
+        <v>50</v>
+      </c>
       <c r="J15" s="37"/>
       <c r="K15" s="67"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="86"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="83"/>
       <c r="P15" s="3"/>
     </row>
     <row r="16" spans="1:23" ht="14.4">
@@ -2097,12 +2128,12 @@
       <c r="G16" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="113"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="109"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="147"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="141"/>
       <c r="N16" s="18"/>
       <c r="P16" s="3"/>
     </row>
@@ -2126,12 +2157,12 @@
       <c r="G17" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="108"/>
-      <c r="M17" s="109"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="141"/>
       <c r="N17" s="18"/>
       <c r="P17" s="3"/>
     </row>
@@ -2155,27 +2186,27 @@
       <c r="G18" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="116"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="111"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="143"/>
       <c r="N18" s="18"/>
       <c r="P18" s="3"/>
     </row>
     <row r="19" spans="1:16" ht="21" customHeight="1">
-      <c r="A19" s="127"/>
+      <c r="A19" s="132"/>
       <c r="B19" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
       <c r="H19" s="46" t="s">
         <v>36</v>
       </c>
@@ -2198,21 +2229,21 @@
       <c r="P19" s="3"/>
     </row>
     <row r="20" spans="1:16" ht="409.05" customHeight="1">
-      <c r="A20" s="127"/>
+      <c r="A20" s="132"/>
       <c r="B20" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="128"/>
-      <c r="D20" s="129"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="129"/>
-      <c r="K20" s="129"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="130"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="135"/>
       <c r="N20" s="18"/>
     </row>
     <row r="21" spans="1:16" ht="14.4">
@@ -2258,19 +2289,19 @@
       <c r="B22" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="131" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
-      <c r="M22" s="132"/>
+      <c r="C22" s="136" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="137"/>
       <c r="N22" s="18"/>
     </row>
     <row r="23" spans="1:16" ht="14.4">
@@ -2318,17 +2349,17 @@
       <c r="B24" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
-      <c r="J24" s="133"/>
-      <c r="K24" s="133"/>
-      <c r="L24" s="133"/>
-      <c r="M24" s="134"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="138"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="139"/>
       <c r="N24" s="18"/>
     </row>
     <row r="25" spans="1:16" s="4" customFormat="1" ht="25.95" customHeight="1">
@@ -2412,69 +2443,69 @@
     <row r="29" spans="1:16" s="4" customFormat="1" ht="15.6">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="77"/>
-      <c r="E29" s="78" t="s">
+      <c r="D29" s="74"/>
+      <c r="E29" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="76"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="76" t="s">
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="I29" s="77"/>
-      <c r="J29" s="76" t="s">
+      <c r="I29" s="74"/>
+      <c r="J29" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="K29" s="76"/>
-      <c r="L29" s="76" t="s">
+      <c r="K29" s="73"/>
+      <c r="L29" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="M29" s="82"/>
+      <c r="M29" s="79"/>
       <c r="N29" s="18"/>
     </row>
     <row r="30" spans="1:16" s="5" customFormat="1" ht="18" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="77" t="s">
+      <c r="C30" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77" t="s">
+      <c r="D30" s="74"/>
+      <c r="E30" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="76" t="s">
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="76"/>
-      <c r="J30" s="77" t="s">
+      <c r="I30" s="73"/>
+      <c r="J30" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="K30" s="77"/>
-      <c r="L30" s="77" t="s">
+      <c r="K30" s="74"/>
+      <c r="L30" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="M30" s="82"/>
+      <c r="M30" s="79"/>
       <c r="N30" s="18"/>
     </row>
     <row r="31" spans="1:16" ht="15">
       <c r="A31" s="18"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="84"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="81"/>
       <c r="N31" s="18"/>
     </row>
     <row r="32" spans="1:16" ht="17.399999999999999">
@@ -2525,22 +2556,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="O8:W8"/>
-    <mergeCell ref="O11:W11"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:M5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="C22:M22"/>
-    <mergeCell ref="C24:M24"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="L18:M18"/>
@@ -2553,6 +2568,22 @@
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="C22:M22"/>
+    <mergeCell ref="C24:M24"/>
+    <mergeCell ref="O8:W8"/>
+    <mergeCell ref="O11:W11"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <conditionalFormatting sqref="E11:F13 E14:E15">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -2575,6 +2606,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71656f95-af41-4770-8c4c-40f2ab2a9f4d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bb65e7c3-e26b-457e-979a-f0bdf4b686f7" xsi:nil="true"/>
+    <DateandTime xmlns="71656f95-af41-4770-8c4c-40f2ab2a9f4d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100223CED9C53918F449F341C0471E40D48" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e131b66a29444f19405a36d79cd6bc23">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71656f95-af41-4770-8c4c-40f2ab2a9f4d" xmlns:ns3="bb65e7c3-e26b-457e-979a-f0bdf4b686f7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fd5d181d26f45a3c965d4872d012ae40" ns2:_="" ns3:_="">
     <xsd:import namespace="71656f95-af41-4770-8c4c-40f2ab2a9f4d"/>
@@ -2835,28 +2887,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28894CD6-A6E1-495A-B4D6-82EEE9A5BFE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="bb65e7c3-e26b-457e-979a-f0bdf4b686f7"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="71656f95-af41-4770-8c4c-40f2ab2a9f4d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71656f95-af41-4770-8c4c-40f2ab2a9f4d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bb65e7c3-e26b-457e-979a-f0bdf4b686f7" xsi:nil="true"/>
-    <DateandTime xmlns="71656f95-af41-4770-8c4c-40f2ab2a9f4d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9DBE0BC-02BA-41C1-A58E-2880BA9FC79E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19111247-A990-4B42-9A2F-A0B34531515A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2873,29 +2929,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9DBE0BC-02BA-41C1-A58E-2880BA9FC79E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28894CD6-A6E1-495A-B4D6-82EEE9A5BFE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="bb65e7c3-e26b-457e-979a-f0bdf4b686f7"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="71656f95-af41-4770-8c4c-40f2ab2a9f4d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>